--- a/data/trans_orig/P33_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>365244</t>
+          <t>366869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>399471</t>
+          <t>399896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>235136</t>
+          <t>235973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>262460</t>
+          <t>263742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>611351</t>
+          <t>610927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>656313</t>
+          <t>655099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67291</t>
+          <t>66866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101518</t>
+          <t>99893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71544</t>
+          <t>70707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117130</t>
+          <t>118344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162092</t>
+          <t>162516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>299112</t>
+          <t>298526</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>328217</t>
+          <t>326477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>288907</t>
+          <t>287863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>318294</t>
+          <t>318413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>596758</t>
+          <t>598037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>638612</t>
+          <t>638854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>37545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64910</t>
+          <t>65496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52635</t>
+          <t>52516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82022</t>
+          <t>83066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96339</t>
+          <t>96097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138193</t>
+          <t>136914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>414581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>450876</t>
+          <t>451985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109586</t>
+          <t>109831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132808</t>
+          <t>132798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>532678</t>
+          <t>531478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>576311</t>
+          <t>576051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85939</t>
+          <t>84830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123834</t>
+          <t>122234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31753</t>
+          <t>31763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>54730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125065</t>
+          <t>125325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168698</t>
+          <t>169898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>914718</t>
+          <t>919638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>972783</t>
+          <t>976414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>535279</t>
+          <t>534404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>577210</t>
+          <t>576262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1469367</t>
+          <t>1469949</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1541750</t>
+          <t>1540631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243702</t>
+          <t>240071</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301767</t>
+          <t>296847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129963</t>
+          <t>130911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171894</t>
+          <t>172769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>381908</t>
+          <t>383027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>454291</t>
+          <t>453709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>258332</t>
+          <t>257986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>288853</t>
+          <t>287010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>407206</t>
+          <t>407155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>448765</t>
+          <t>450182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>674578</t>
+          <t>672798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>726544</t>
+          <t>726406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56645</t>
+          <t>58488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87166</t>
+          <t>87512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119987</t>
+          <t>118570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161546</t>
+          <t>161597</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187706</t>
+          <t>187844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>239672</t>
+          <t>241452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>260890</t>
+          <t>260606</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>279156</t>
+          <t>279338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>855980</t>
+          <t>856251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>919279</t>
+          <t>921333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1127063</t>
+          <t>1127499</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1194384</t>
+          <t>1192009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32779</t>
+          <t>33063</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318691</t>
+          <t>316637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>381990</t>
+          <t>381719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>337255</t>
+          <t>339630</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>404576</t>
+          <t>404140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2581307</t>
+          <t>2581887</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2667413</t>
+          <t>2667541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2502467</t>
+          <t>2496776</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2602549</t>
+          <t>2596288</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5109629</t>
+          <t>5108938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5239330</t>
+          <t>5242424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>555839</t>
+          <t>555711</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>641945</t>
+          <t>641365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>753516</t>
+          <t>759777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>853598</t>
+          <t>859289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1339987</t>
+          <t>1336893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1469688</t>
+          <t>1470379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>312212</t>
+          <t>313976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>349020</t>
+          <t>351198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>233748</t>
+          <t>236288</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>264073</t>
+          <t>267211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>559327</t>
+          <t>557631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>607035</t>
+          <t>605411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88191</t>
+          <t>86013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124999</t>
+          <t>123235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50381</t>
+          <t>47243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80706</t>
+          <t>78166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144630</t>
+          <t>146254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192338</t>
+          <t>194034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>290248</t>
+          <t>290525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>328699</t>
+          <t>329467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>224590</t>
+          <t>226004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259780</t>
+          <t>259631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>527652</t>
+          <t>526726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>578230</t>
+          <t>580259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89163</t>
+          <t>88395</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127614</t>
+          <t>127337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78231</t>
+          <t>78380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113421</t>
+          <t>112007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177643</t>
+          <t>175614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228221</t>
+          <t>229147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>432849</t>
+          <t>433296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>481419</t>
+          <t>481742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167320</t>
+          <t>166008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>196652</t>
+          <t>195972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>613307</t>
+          <t>609592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>668149</t>
+          <t>664367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145944</t>
+          <t>145621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194514</t>
+          <t>194067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60127</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89459</t>
+          <t>90771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215994</t>
+          <t>219776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270836</t>
+          <t>274551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>806888</t>
+          <t>806803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>867897</t>
+          <t>867625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>516522</t>
+          <t>517432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>568419</t>
+          <t>568632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1342750</t>
+          <t>1337734</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1421317</t>
+          <t>1418575</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284107</t>
+          <t>284379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345116</t>
+          <t>345201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198238</t>
+          <t>198025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>250135</t>
+          <t>249225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>497344</t>
+          <t>500086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>575911</t>
+          <t>580927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>345258</t>
+          <t>343845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>384632</t>
+          <t>383791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>446160</t>
+          <t>444811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>500712</t>
+          <t>500169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>799175</t>
+          <t>799415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>871390</t>
+          <t>870135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124656</t>
+          <t>125497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>165443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>259828</t>
+          <t>260371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>314380</t>
+          <t>315729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398438</t>
+          <t>399693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>470653</t>
+          <t>470413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>206563</t>
+          <t>206474</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>231469</t>
+          <t>231846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>662027</t>
+          <t>664011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>728714</t>
+          <t>727121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>880009</t>
+          <t>880373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>951717</t>
+          <t>951164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59365</t>
+          <t>59454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>375618</t>
+          <t>377211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>442305</t>
+          <t>440321</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>418543</t>
+          <t>419096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>490251</t>
+          <t>489887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2468423</t>
+          <t>2471922</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2576127</t>
+          <t>2579532</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2334682</t>
+          <t>2329612</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2446693</t>
+          <t>2448885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4831804</t>
+          <t>4837660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4988530</t>
+          <t>4992731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>833528</t>
+          <t>830123</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>941232</t>
+          <t>937733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1094081</t>
+          <t>1091889</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1206092</t>
+          <t>1211162</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1961899</t>
+          <t>1957698</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2118625</t>
+          <t>2112769</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>317001</t>
+          <t>317599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>352412</t>
+          <t>353888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>260452</t>
+          <t>259792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290331</t>
+          <t>291809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>589411</t>
+          <t>592197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>637597</t>
+          <t>638221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76680</t>
+          <t>75204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112091</t>
+          <t>111493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56724</t>
+          <t>55246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86603</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138550</t>
+          <t>137926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186736</t>
+          <t>183950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>258472</t>
+          <t>260420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294241</t>
+          <t>295661</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>280322</t>
+          <t>279805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>312063</t>
+          <t>312012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>550029</t>
+          <t>550032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>599206</t>
+          <t>596506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82074</t>
+          <t>80654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117843</t>
+          <t>115895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60210</t>
+          <t>60261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91951</t>
+          <t>92468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149382</t>
+          <t>152082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198559</t>
+          <t>198556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>369732</t>
+          <t>369398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>409516</t>
+          <t>409776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110787</t>
+          <t>109094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133752</t>
+          <t>133934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>491637</t>
+          <t>487976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>535706</t>
+          <t>536024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110811</t>
+          <t>110551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150595</t>
+          <t>150929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51209</t>
+          <t>52902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146617</t>
+          <t>146299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190686</t>
+          <t>194347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>837262</t>
+          <t>832320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>895842</t>
+          <t>895069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>556605</t>
+          <t>556319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>608180</t>
+          <t>611728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1408282</t>
+          <t>1411496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1489447</t>
+          <t>1491349</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>250647</t>
+          <t>251420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309227</t>
+          <t>314169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214960</t>
+          <t>211412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>266535</t>
+          <t>266821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>480182</t>
+          <t>478280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>561347</t>
+          <t>558133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>458750</t>
+          <t>458735</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>501805</t>
+          <t>500862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>480045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>531954</t>
+          <t>530617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>952831</t>
+          <t>955166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1020046</t>
+          <t>1018196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117783</t>
+          <t>118726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160838</t>
+          <t>160853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204085</t>
+          <t>205422</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254858</t>
+          <t>255994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335580</t>
+          <t>337430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>402795</t>
+          <t>400460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>228862</t>
+          <t>229286</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>254258</t>
+          <t>253914</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>696249</t>
+          <t>694971</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>758903</t>
+          <t>758740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>934467</t>
+          <t>933991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1006207</t>
+          <t>1003677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32887</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58283</t>
+          <t>57859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317650</t>
+          <t>317813</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>380304</t>
+          <t>381582</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>357491</t>
+          <t>360021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>429231</t>
+          <t>429707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2546660</t>
+          <t>2542455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2646136</t>
+          <t>2646167</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2457788</t>
+          <t>2457982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2570370</t>
+          <t>2572920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5040063</t>
+          <t>5037975</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5187960</t>
+          <t>5191049</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>732820</t>
+          <t>732789</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>832296</t>
+          <t>836501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>946686</t>
+          <t>944136</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1059268</t>
+          <t>1059074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1708052</t>
+          <t>1704963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1855949</t>
+          <t>1858037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>360717</t>
+          <t>358394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>400107</t>
+          <t>398318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>303393</t>
+          <t>302981</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>335512</t>
+          <t>334831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>676263</t>
+          <t>675888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>727052</t>
+          <t>723247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95047</t>
+          <t>96836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134437</t>
+          <t>136760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106570</t>
+          <t>107251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138689</t>
+          <t>139101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210184</t>
+          <t>213989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>260973</t>
+          <t>261348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>321773</t>
+          <t>322192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>359366</t>
+          <t>359561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>257875</t>
+          <t>254734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286340</t>
+          <t>284951</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>591637</t>
+          <t>593928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>638815</t>
+          <t>637866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87469</t>
+          <t>87274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125062</t>
+          <t>124643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89378</t>
+          <t>90767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117843</t>
+          <t>120984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183738</t>
+          <t>184687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>228625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>435759</t>
+          <t>434480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>607444</t>
+          <t>607491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104018</t>
+          <t>104454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121981</t>
+          <t>122281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>548314</t>
+          <t>553894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>741776</t>
+          <t>743127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52482</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224167</t>
+          <t>225446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>39883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58146</t>
+          <t>57710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80314</t>
+          <t>78963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273776</t>
+          <t>268196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>684482</t>
+          <t>685389</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>747047</t>
+          <t>745426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263162</t>
+          <t>243939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>636537</t>
+          <t>640912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>816648</t>
+          <t>823090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1372558</t>
+          <t>1374480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234298</t>
+          <t>235919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296863</t>
+          <t>295956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319275</t>
+          <t>314900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>692650</t>
+          <t>711873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>564600</t>
+          <t>562678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1120510</t>
+          <t>1114068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>315302</t>
+          <t>317761</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>354173</t>
+          <t>355252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,47 +10025,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>69,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>561139</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>524997</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>626075</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>69,39%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>561139</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>522661</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>629623</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>69,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>855181</t>
+          <t>857153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>958644</t>
+          <t>960427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100201</t>
+          <t>99122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139072</t>
+          <t>136613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,47 +10138,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>30,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>247535</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>182599</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>283677</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>30,61%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>247535</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>179051</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>286013</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304404</t>
+          <t>302621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407867</t>
+          <t>405895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190053</t>
+          <t>191138</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>225316</t>
+          <t>224927</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>508851</t>
+          <t>507085</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>549547</t>
+          <t>548256</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>712603</t>
+          <t>714866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>766084</t>
+          <t>766525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46244</t>
+          <t>45159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>182717</t>
+          <t>184008</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223413</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202478</t>
+          <t>202037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>255959</t>
+          <t>253696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2433971</t>
+          <t>2437276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2704761</t>
+          <t>2760795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1793159</t>
+          <t>1791315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2456851</t>
+          <t>2459848</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4270088</t>
+          <t>4337272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5019138</t>
+          <t>5025940</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>569171</t>
+          <t>513137</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>839961</t>
+          <t>836656</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1019864</t>
+          <t>1016867</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1683556</t>
+          <t>1685400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1731509</t>
+          <t>1724707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2480559</t>
+          <t>2413375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>366869</t>
+          <t>365013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>399896</t>
+          <t>401203</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>235973</t>
+          <t>236249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>263742</t>
+          <t>262911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>610927</t>
+          <t>612173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>655099</t>
+          <t>653684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66866</t>
+          <t>65559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>101749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42938</t>
+          <t>43769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70707</t>
+          <t>70431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118344</t>
+          <t>119759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162516</t>
+          <t>161270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>298526</t>
+          <t>298354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>326477</t>
+          <t>328353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>287863</t>
+          <t>290107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>318413</t>
+          <t>318405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>598037</t>
+          <t>596360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>638854</t>
+          <t>637659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37545</t>
+          <t>35669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65496</t>
+          <t>65668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52516</t>
+          <t>52524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83066</t>
+          <t>80822</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96097</t>
+          <t>97292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136914</t>
+          <t>138591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>414581</t>
+          <t>412861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>451985</t>
+          <t>449390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109831</t>
+          <t>109215</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132798</t>
+          <t>131935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>531478</t>
+          <t>533940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>576051</t>
+          <t>577983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84830</t>
+          <t>87425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>122234</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31763</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54730</t>
+          <t>55346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125325</t>
+          <t>123393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169898</t>
+          <t>167436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>919638</t>
+          <t>914830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>976414</t>
+          <t>974989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>534404</t>
+          <t>531252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>576262</t>
+          <t>574808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1469949</t>
+          <t>1468449</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1540631</t>
+          <t>1543649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240071</t>
+          <t>241496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296847</t>
+          <t>301655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130911</t>
+          <t>132365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172769</t>
+          <t>175921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383027</t>
+          <t>380009</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>453709</t>
+          <t>455209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>257986</t>
+          <t>256093</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287010</t>
+          <t>286795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>407155</t>
+          <t>406051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>450182</t>
+          <t>449135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>672798</t>
+          <t>673094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>726406</t>
+          <t>725448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58488</t>
+          <t>58703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>89405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118570</t>
+          <t>119617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161597</t>
+          <t>162701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187844</t>
+          <t>188802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241452</t>
+          <t>241156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>260606</t>
+          <t>260379</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>279338</t>
+          <t>279530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>856251</t>
+          <t>856276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>921333</t>
+          <t>920023</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1127499</t>
+          <t>1123331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1192009</t>
+          <t>1194058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14331</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316637</t>
+          <t>317947</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>381719</t>
+          <t>381694</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>339630</t>
+          <t>337581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>404140</t>
+          <t>408308</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2581887</t>
+          <t>2581476</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2667541</t>
+          <t>2665998</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2496776</t>
+          <t>2498629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2596288</t>
+          <t>2595739</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5108938</t>
+          <t>5101839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5242424</t>
+          <t>5237043</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>555711</t>
+          <t>557254</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>641365</t>
+          <t>641776</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>759777</t>
+          <t>760326</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>859289</t>
+          <t>857436</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1336893</t>
+          <t>1342274</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1470379</t>
+          <t>1477478</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313976</t>
+          <t>313538</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351198</t>
+          <t>352384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>236288</t>
+          <t>235983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267211</t>
+          <t>264315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>557631</t>
+          <t>560073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>605411</t>
+          <t>607228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86013</t>
+          <t>84827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123235</t>
+          <t>123673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47243</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78166</t>
+          <t>78471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146254</t>
+          <t>144437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194034</t>
+          <t>191592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>290525</t>
+          <t>293208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>329467</t>
+          <t>330254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>224075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259631</t>
+          <t>258945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>526726</t>
+          <t>528698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>580259</t>
+          <t>582330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88395</t>
+          <t>87608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127337</t>
+          <t>124654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78380</t>
+          <t>79066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112007</t>
+          <t>113936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>175614</t>
+          <t>173543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>229147</t>
+          <t>227175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>433296</t>
+          <t>434107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>481742</t>
+          <t>481180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166008</t>
+          <t>164430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195972</t>
+          <t>195608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>609592</t>
+          <t>610890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>664367</t>
+          <t>666046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145621</t>
+          <t>146183</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194067</t>
+          <t>193256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>61171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90771</t>
+          <t>92349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219776</t>
+          <t>218097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>274551</t>
+          <t>273253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>806803</t>
+          <t>805127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>867625</t>
+          <t>869053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>517432</t>
+          <t>517053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>568632</t>
+          <t>569753</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1337734</t>
+          <t>1339637</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1418575</t>
+          <t>1420716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284379</t>
+          <t>282951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345201</t>
+          <t>346877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198025</t>
+          <t>196904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>249225</t>
+          <t>249604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>500086</t>
+          <t>497945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>580927</t>
+          <t>579024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>343845</t>
+          <t>345176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>383791</t>
+          <t>384820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>444811</t>
+          <t>446180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>500169</t>
+          <t>499972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>799415</t>
+          <t>805203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>870135</t>
+          <t>873023</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125497</t>
+          <t>124468</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165443</t>
+          <t>164112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>260371</t>
+          <t>260568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>315729</t>
+          <t>314360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>399693</t>
+          <t>396805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>470413</t>
+          <t>464625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>206474</t>
+          <t>207517</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>231846</t>
+          <t>231739</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>664011</t>
+          <t>664488</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>727121</t>
+          <t>727233</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>880373</t>
+          <t>881381</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>951164</t>
+          <t>951480</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34082</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59454</t>
+          <t>58411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>377211</t>
+          <t>377099</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>440321</t>
+          <t>439844</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>419096</t>
+          <t>418780</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>489887</t>
+          <t>488879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2471922</t>
+          <t>2470748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2579532</t>
+          <t>2577937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2329612</t>
+          <t>2334195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2448885</t>
+          <t>2447148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4837660</t>
+          <t>4835294</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4992731</t>
+          <t>4993194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>830123</t>
+          <t>831718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>937733</t>
+          <t>938907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1091889</t>
+          <t>1093626</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1211162</t>
+          <t>1206579</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1957698</t>
+          <t>1957235</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2112769</t>
+          <t>2115135</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>317599</t>
+          <t>318221</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>353888</t>
+          <t>353016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>259792</t>
+          <t>261107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291809</t>
+          <t>291974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>592197</t>
+          <t>590371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>638221</t>
+          <t>637004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75204</t>
+          <t>76076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111493</t>
+          <t>110871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55246</t>
+          <t>55081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>85948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137926</t>
+          <t>139143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183950</t>
+          <t>185776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>260420</t>
+          <t>259991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295661</t>
+          <t>296197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>279805</t>
+          <t>278394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>312012</t>
+          <t>312305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>550032</t>
+          <t>548808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>596506</t>
+          <t>597911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80654</t>
+          <t>80118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115895</t>
+          <t>116324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>59968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92468</t>
+          <t>93879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152082</t>
+          <t>150677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198556</t>
+          <t>199780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>369398</t>
+          <t>368567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>409776</t>
+          <t>408741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109094</t>
+          <t>110659</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133934</t>
+          <t>133142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>487976</t>
+          <t>490775</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>536024</t>
+          <t>536498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110551</t>
+          <t>111586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150929</t>
+          <t>151760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52902</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146299</t>
+          <t>145825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194347</t>
+          <t>191548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>832320</t>
+          <t>834274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>895069</t>
+          <t>893343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>556319</t>
+          <t>557005</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>611728</t>
+          <t>610076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1411496</t>
+          <t>1413676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1491349</t>
+          <t>1493385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251420</t>
+          <t>253146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314169</t>
+          <t>312215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211412</t>
+          <t>213064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>266821</t>
+          <t>266135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>478280</t>
+          <t>476244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>558133</t>
+          <t>555953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>458735</t>
+          <t>460196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>500862</t>
+          <t>500856</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>480045</t>
+          <t>484251</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>530617</t>
+          <t>533023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>955166</t>
+          <t>955022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1018196</t>
+          <t>1020938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118726</t>
+          <t>118732</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160853</t>
+          <t>159392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205422</t>
+          <t>203016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>255994</t>
+          <t>251788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337430</t>
+          <t>334688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400460</t>
+          <t>400604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>229286</t>
+          <t>229142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>253914</t>
+          <t>253958</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>694971</t>
+          <t>695405</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>758740</t>
+          <t>759247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>933991</t>
+          <t>934739</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1003677</t>
+          <t>1004673</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33231</t>
+          <t>33187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57859</t>
+          <t>58003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317813</t>
+          <t>317306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>381582</t>
+          <t>381148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>360021</t>
+          <t>359025</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>429707</t>
+          <t>428959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2542455</t>
+          <t>2548673</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2646167</t>
+          <t>2647719</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2457982</t>
+          <t>2459329</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2572920</t>
+          <t>2566475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5037975</t>
+          <t>5043337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5191049</t>
+          <t>5189039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>732789</t>
+          <t>731237</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>836501</t>
+          <t>830283</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>944136</t>
+          <t>950581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1059074</t>
+          <t>1057727</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1704963</t>
+          <t>1706973</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1858037</t>
+          <t>1852675</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>380208</t>
+          <t>416727</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>358394</t>
+          <t>395115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>398318</t>
+          <t>435907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>320436</t>
+          <t>351128</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>302981</t>
+          <t>334847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>334831</t>
+          <t>368717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>700645</t>
+          <t>767855</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>675888</t>
+          <t>735240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>723247</t>
+          <t>792280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114946</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96836</t>
+          <t>104172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136760</t>
+          <t>144964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>121646</t>
+          <t>131260</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107251</t>
+          <t>113671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139101</t>
+          <t>147541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>236591</t>
+          <t>254612</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>213989</t>
+          <t>230187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>261348</t>
+          <t>287227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>495154</t>
+          <t>540079</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>495154</t>
+          <t>540079</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>495154</t>
+          <t>540079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>442082</t>
+          <t>482388</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>442082</t>
+          <t>482388</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>442082</t>
+          <t>482388</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>937236</t>
+          <t>1022467</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>937236</t>
+          <t>1022467</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>937236</t>
+          <t>1022467</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>343949</t>
+          <t>369277</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>322192</t>
+          <t>349874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>359561</t>
+          <t>386363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>271370</t>
+          <t>300550</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>254734</t>
+          <t>284108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>284951</t>
+          <t>316726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>615320</t>
+          <t>669828</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>593928</t>
+          <t>647006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>637866</t>
+          <t>695688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>102886</t>
+          <t>107384</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87274</t>
+          <t>90298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124643</t>
+          <t>126787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>104348</t>
+          <t>114510</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>98334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120984</t>
+          <t>130952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>207233</t>
+          <t>221894</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184687</t>
+          <t>196034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228625</t>
+          <t>244716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>446835</t>
+          <t>476661</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>446835</t>
+          <t>476661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>446835</t>
+          <t>476661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>415060</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>415060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>415060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>822553</t>
+          <t>891722</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>822553</t>
+          <t>891722</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>822553</t>
+          <t>891722</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>524027</t>
+          <t>312369</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>434480</t>
+          <t>290829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>607491</t>
+          <t>331637</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113661</t>
+          <t>129708</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104454</t>
+          <t>119966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122281</t>
+          <t>140190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>637688</t>
+          <t>442077</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>553894</t>
+          <t>419160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>743127</t>
+          <t>465362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>135899</t>
+          <t>149685</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>130417</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225446</t>
+          <t>171225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48503</t>
+          <t>52865</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39883</t>
+          <t>42383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57710</t>
+          <t>62607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>184402</t>
+          <t>202550</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78963</t>
+          <t>179265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>268196</t>
+          <t>225467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>659926</t>
+          <t>462054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>659926</t>
+          <t>462054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>659926</t>
+          <t>462054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>162164</t>
+          <t>182573</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>162164</t>
+          <t>182573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162164</t>
+          <t>182573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>822090</t>
+          <t>644627</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>822090</t>
+          <t>644627</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>822090</t>
+          <t>644627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>718736</t>
+          <t>802647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>685389</t>
+          <t>769052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>745426</t>
+          <t>828849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>495400</t>
+          <t>551358</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>243939</t>
+          <t>527315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>640912</t>
+          <t>573848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1214136</t>
+          <t>1354004</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>823090</t>
+          <t>1314556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1374480</t>
+          <t>1391462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262609</t>
+          <t>276354</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235919</t>
+          <t>250152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295956</t>
+          <t>309949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>460412</t>
+          <t>285303</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314900</t>
+          <t>262813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>711873</t>
+          <t>309346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>723022</t>
+          <t>561658</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562678</t>
+          <t>524200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1114068</t>
+          <t>601106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>981345</t>
+          <t>1079001</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>981345</t>
+          <t>1079001</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>981345</t>
+          <t>1079001</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>955812</t>
+          <t>836661</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>955812</t>
+          <t>836661</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>955812</t>
+          <t>836661</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1937158</t>
+          <t>1915662</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1937158</t>
+          <t>1915662</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1937158</t>
+          <t>1915662</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>336422</t>
+          <t>408072</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>317761</t>
+          <t>385796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>355252</t>
+          <t>429997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>525564</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>524997</t>
+          <t>502281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>626075</t>
+          <t>546627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>897560</t>
+          <t>933635</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>857153</t>
+          <t>902074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>960427</t>
+          <t>962283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>117952</t>
+          <t>139602</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99122</t>
+          <t>117677</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136613</t>
+          <t>161878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>247535</t>
+          <t>272405</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182599</t>
+          <t>251342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>283677</t>
+          <t>295688</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>365488</t>
+          <t>412008</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302621</t>
+          <t>383360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405895</t>
+          <t>443569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>454374</t>
+          <t>547674</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>454374</t>
+          <t>547674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>454374</t>
+          <t>547674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>808674</t>
+          <t>797969</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>808674</t>
+          <t>797969</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>808674</t>
+          <t>797969</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1263048</t>
+          <t>1345643</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1263048</t>
+          <t>1345643</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1263048</t>
+          <t>1345643</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>213114</t>
+          <t>210039</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>191138</t>
+          <t>191754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>224927</t>
+          <t>221715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>529446</t>
+          <t>587208</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>507085</t>
+          <t>563089</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>548256</t>
+          <t>609907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>742561</t>
+          <t>797247</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>714866</t>
+          <t>767651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>766525</t>
+          <t>823808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>23579</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45159</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>202818</t>
+          <t>226226</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184008</t>
+          <t>203527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225179</t>
+          <t>250345</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>226001</t>
+          <t>249805</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202037</t>
+          <t>223244</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253696</t>
+          <t>279401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>236297</t>
+          <t>233618</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>236297</t>
+          <t>233618</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>236297</t>
+          <t>233618</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>732264</t>
+          <t>813434</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>732264</t>
+          <t>813434</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>732264</t>
+          <t>813434</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>968562</t>
+          <t>1047052</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>968562</t>
+          <t>1047052</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>968562</t>
+          <t>1047052</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2516458</t>
+          <t>2519131</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2437276</t>
+          <t>2467331</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2760795</t>
+          <t>2573425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2291453</t>
+          <t>2445515</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1791315</t>
+          <t>2397336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2459848</t>
+          <t>2494032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4807910</t>
+          <t>4964645</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4337272</t>
+          <t>4890479</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5025940</t>
+          <t>5031247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
+          <t>72,3%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>71,22%</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>64,25%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>757474</t>
+          <t>819956</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>513137</t>
+          <t>765662</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>836656</t>
+          <t>871756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1185262</t>
+          <t>1082570</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1016867</t>
+          <t>1034053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1685400</t>
+          <t>1130749</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1942737</t>
+          <t>1902527</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1724707</t>
+          <t>1835925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2413375</t>
+          <t>1976693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
+          <t>27,7%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>28,78%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3273932</t>
+          <t>3339087</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3273932</t>
+          <t>3339087</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3273932</t>
+          <t>3339087</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3476715</t>
+          <t>3528085</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3476715</t>
+          <t>3528085</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3476715</t>
+          <t>3528085</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6750647</t>
+          <t>6867172</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6750647</t>
+          <t>6867172</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6750647</t>
+          <t>6867172</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
